--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,16 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>Fechas_Semanal</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Coincidencias_Intermedia</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Coincidencias_Semanal</t>
         </is>
       </c>
     </row>
@@ -501,6 +511,8 @@
           <t>2026-03-03, 2026-03-04</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +534,8 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +557,8 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +596,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +631,8 @@
           <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +654,8 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,6 +705,16 @@
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -724,6 +760,8 @@
           <t>2026-03-10</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,6 +813,12 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-02, 2026-03-04, 2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
     </row>
@@ -806,6 +850,8 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -843,6 +889,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -880,6 +932,8 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -917,6 +971,8 @@
           <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -938,6 +994,8 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -967,6 +1025,8 @@
           <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-04, 2026-03-04</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1008,6 +1068,8 @@
           <t>2026-03-09</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1061,6 +1123,16 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1102,6 +1174,16 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
@@ -1127,6 +1209,8 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1152,6 +1236,8 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1205,6 +1291,12 @@
           <t>2026-03-10</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1226,6 +1318,8 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1247,6 +1341,8 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1296,6 +1392,16 @@
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -1337,6 +1443,12 @@
           <t>2026-03-04, 2026-03-04, 2026-03-06</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1366,6 +1478,8 @@
           <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1403,6 +1517,8 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1424,6 +1540,8 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1475,6 +1593,16 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1498,6 +1626,8 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1547,6 +1677,16 @@
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -1580,6 +1720,8 @@
           <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1621,6 +1763,12 @@
           <t>2026-03-03, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1658,6 +1806,12 @@
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1687,6 +1841,8 @@
           <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1736,6 +1892,16 @@
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -1761,6 +1927,8 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1814,6 +1982,12 @@
           <t>2026-03-02, 2026-03-05</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1863,6 +2037,16 @@
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
@@ -1904,6 +2088,12 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,25 +1630,21 @@
       <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1658,12 +1654,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1673,24 +1669,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1700,28 +1692,60 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1731,43 +1755,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1778,34 +1786,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -1821,27 +1833,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1852,60 +1876,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1915,20 +1907,60 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1938,56 +1970,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-05</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1997,7 +1993,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2008,17 +2004,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2028,27 +2024,23 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2052,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2069,15 +2061,31 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>2026-03-05</t>
@@ -2085,15 +2093,62 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -582,7 +582,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -691,12 +691,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -746,7 +746,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -875,7 +875,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -957,7 +957,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1677,11 +1677,7 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1804,7 +1800,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1851,7 +1847,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -1933,7 +1929,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -582,7 +582,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -691,12 +691,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -746,7 +746,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -818,7 +818,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -957,7 +957,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-10, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1677,7 +1677,11 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1714,7 +1718,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1800,7 +1804,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1847,7 +1851,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -1929,7 +1933,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -582,7 +582,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -691,12 +691,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -746,7 +746,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -818,7 +818,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -957,7 +957,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-10, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1677,11 +1677,7 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1804,7 +1800,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1851,7 +1847,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -1933,7 +1929,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -574,7 +574,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1796,14 +1796,24 @@
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.3958333333333333</v>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05</t>
@@ -1819,7 +1829,11 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,36 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Coincidencias_Semanal</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Indicador_Intermedia</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Indicador_Semanal</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Count_Posibles_Intermedia</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Count_Coincidencias_Intermedia</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Count_Posibles_Semanal</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Count_Coincidencias_Semanal</t>
         </is>
       </c>
     </row>
@@ -513,6 +543,24 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -536,6 +584,24 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,6 +625,24 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -602,6 +686,24 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>250</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -633,6 +735,24 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -656,6 +776,24 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -718,6 +856,24 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="N8" t="n">
+        <v>250</v>
+      </c>
+      <c r="O8" t="n">
+        <v>400</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -762,6 +918,24 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -820,6 +994,24 @@
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -852,6 +1044,24 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -895,6 +1105,24 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -934,6 +1162,24 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -973,6 +1219,24 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -996,6 +1260,24 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1027,6 +1309,24 @@
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1070,6 +1370,24 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1133,6 +1451,24 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="N18" t="n">
+        <v>400</v>
+      </c>
+      <c r="O18" t="n">
+        <v>400</v>
+      </c>
+      <c r="P18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1187,6 +1523,24 @@
         <is>
           <t>2026-03-06</t>
         </is>
+      </c>
+      <c r="N19" t="n">
+        <v>400</v>
+      </c>
+      <c r="O19" t="n">
+        <v>400</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1211,6 +1565,24 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1238,6 +1610,24 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1297,6 +1687,24 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>400</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1320,6 +1728,24 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1343,6 +1769,24 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1405,6 +1849,24 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="N25" t="n">
+        <v>450</v>
+      </c>
+      <c r="O25" t="n">
+        <v>400</v>
+      </c>
+      <c r="P25" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>8</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1449,6 +1911,24 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>450</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1480,6 +1960,24 @@
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1519,6 +2017,24 @@
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1542,6 +2058,24 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1604,6 +2138,24 @@
         <is>
           <t>2026-03-10</t>
         </is>
+      </c>
+      <c r="N30" t="n">
+        <v>250</v>
+      </c>
+      <c r="O30" t="n">
+        <v>450</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1628,6 +2180,24 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1679,6 +2249,24 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>8</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1741,6 +2329,24 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="N33" t="n">
+        <v>450</v>
+      </c>
+      <c r="O33" t="n">
+        <v>400</v>
+      </c>
+      <c r="P33" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>8</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1773,6 +2379,24 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1833,6 +2457,24 @@
         <is>
           <t>2026-03-04</t>
         </is>
+      </c>
+      <c r="N35" t="n">
+        <v>450</v>
+      </c>
+      <c r="O35" t="n">
+        <v>400</v>
+      </c>
+      <c r="P35" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>8</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1877,6 +2519,24 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>400</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1908,6 +2568,24 @@
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1970,6 +2648,24 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="N38" t="n">
+        <v>400</v>
+      </c>
+      <c r="O38" t="n">
+        <v>400</v>
+      </c>
+      <c r="P38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>8</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1994,6 +2690,24 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2053,6 +2767,24 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>400</v>
+      </c>
+      <c r="P40" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>8</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2115,6 +2847,24 @@
         <is>
           <t>2026-03-07</t>
         </is>
+      </c>
+      <c r="N41" t="n">
+        <v>400</v>
+      </c>
+      <c r="O41" t="n">
+        <v>400</v>
+      </c>
+      <c r="P41" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2159,6 +2909,24 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>400</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="O8" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P8" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="P10" t="n">
         <v>8</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O18" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P18" t="n">
         <v>8</v>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O19" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P19" t="n">
         <v>8</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="O25" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P25" t="n">
         <v>9</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="O30" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="P30" t="n">
         <v>10</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="O33" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P33" t="n">
         <v>9</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="O35" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P35" t="n">
         <v>9</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O38" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P38" t="n">
         <v>8</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P40" t="n">
         <v>8</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O41" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P41" t="n">
         <v>8</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,36 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Coincidencias_Semanal</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Indicador_Intermedia</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Indicador_Semanal</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Count_Posibles_Intermedia</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Count_Coincidencias_Intermedia</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Count_Posibles_Semanal</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Count_Coincidencias_Semanal</t>
         </is>
       </c>
     </row>
@@ -543,24 +513,6 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -584,24 +536,6 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -625,24 +559,6 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -686,24 +602,6 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>125</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -735,24 +633,6 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -776,24 +656,6 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -856,24 +718,6 @@
         <is>
           <t>2026-03-05</t>
         </is>
-      </c>
-      <c r="N8" t="n">
-        <v>125</v>
-      </c>
-      <c r="O8" t="n">
-        <v>200</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -918,24 +762,6 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -994,24 +820,6 @@
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>125</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>10</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1044,24 +852,6 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1105,24 +895,6 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>225</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1162,24 +934,6 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1219,24 +973,6 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1260,24 +996,6 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1309,24 +1027,6 @@
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1370,24 +1070,6 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1451,24 +1133,6 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>200</v>
-      </c>
-      <c r="O18" t="n">
-        <v>200</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>8</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1523,24 +1187,6 @@
         <is>
           <t>2026-03-06</t>
         </is>
-      </c>
-      <c r="N19" t="n">
-        <v>200</v>
-      </c>
-      <c r="O19" t="n">
-        <v>200</v>
-      </c>
-      <c r="P19" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1565,24 +1211,6 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1610,24 +1238,6 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1687,24 +1297,6 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>200</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>8</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1728,24 +1320,6 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1769,24 +1343,6 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1849,24 +1405,6 @@
         <is>
           <t>2026-03-05</t>
         </is>
-      </c>
-      <c r="N25" t="n">
-        <v>225</v>
-      </c>
-      <c r="O25" t="n">
-        <v>200</v>
-      </c>
-      <c r="P25" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1911,24 +1449,6 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>225</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1960,24 +1480,6 @@
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2017,24 +1519,6 @@
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2058,24 +1542,6 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2138,24 +1604,6 @@
         <is>
           <t>2026-03-10</t>
         </is>
-      </c>
-      <c r="N30" t="n">
-        <v>125</v>
-      </c>
-      <c r="O30" t="n">
-        <v>225</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>9</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2180,24 +1628,6 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2249,24 +1679,6 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>8</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2329,24 +1741,6 @@
         <is>
           <t>2026-03-05</t>
         </is>
-      </c>
-      <c r="N33" t="n">
-        <v>225</v>
-      </c>
-      <c r="O33" t="n">
-        <v>200</v>
-      </c>
-      <c r="P33" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>8</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2379,24 +1773,6 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2459,24 +1835,6 @@
         <is>
           <t>2026-03-04</t>
         </is>
-      </c>
-      <c r="N35" t="n">
-        <v>225</v>
-      </c>
-      <c r="O35" t="n">
-        <v>200</v>
-      </c>
-      <c r="P35" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>8</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2521,24 +1879,6 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>200</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2570,24 +1910,6 @@
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2650,24 +1972,6 @@
         <is>
           <t>2026-03-05</t>
         </is>
-      </c>
-      <c r="N38" t="n">
-        <v>200</v>
-      </c>
-      <c r="O38" t="n">
-        <v>200</v>
-      </c>
-      <c r="P38" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>8</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2692,24 +1996,6 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2769,24 +2055,6 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>200</v>
-      </c>
-      <c r="P40" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>8</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2849,24 +2117,6 @@
         <is>
           <t>2026-03-07</t>
         </is>
-      </c>
-      <c r="N41" t="n">
-        <v>200</v>
-      </c>
-      <c r="O41" t="n">
-        <v>200</v>
-      </c>
-      <c r="P41" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>8</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2911,24 +2161,6 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
-        <v>200</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,20 +464,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>ConteoIntermedia</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ConteoSemanal</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Fechas_Intermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fechas_Semanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Coincidencias_Intermedia</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Coincidencias_Semanal</t>
         </is>
@@ -501,18 +511,24 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-04</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,10 +548,16 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -555,10 +577,16 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -586,22 +614,28 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -621,18 +655,24 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-02</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,10 +692,16 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -699,22 +745,28 @@
           <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -750,18 +802,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -805,18 +863,24 @@
           <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-02, 2026-03-04, 2026-03-04, 2026-03-07</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-02, 2026-03-04, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
@@ -840,18 +904,24 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -879,22 +949,28 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,18 +998,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -961,18 +1043,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-05</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -992,10 +1080,16 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1015,18 +1109,24 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-04, 2026-03-04</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-04, 2026-03-04</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1058,18 +1158,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1113,22 +1219,28 @@
           <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -1168,22 +1280,28 @@
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
@@ -1207,10 +1325,16 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1230,14 +1354,20 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1281,22 +1411,28 @@
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1316,10 +1452,16 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1339,10 +1481,16 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1386,22 +1534,28 @@
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -1433,22 +1587,28 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-04</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-04, 2026-03-06</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1468,18 +1628,24 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-10, 2026-03-10</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1511,14 +1677,20 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1538,10 +1710,16 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1585,22 +1763,28 @@
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-10</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
@@ -1624,10 +1808,16 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1667,18 +1857,24 @@
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1722,22 +1918,28 @@
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -1761,18 +1963,24 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1816,22 +2024,28 @@
           <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -1867,18 +2081,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1898,18 +2118,24 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1953,22 +2179,28 @@
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -1992,10 +2224,16 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2039,18 +2277,24 @@
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-05</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -2098,22 +2342,28 @@
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
@@ -2145,22 +2395,28 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,16 @@
       <c r="O1" t="inlineStr">
         <is>
           <t>Coincidencias_Semanal</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ConteoCoincidenciasIntermedia</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
     </row>
@@ -529,6 +539,12 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -558,6 +574,12 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +609,12 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -636,6 +664,12 @@
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -673,6 +707,12 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +742,12 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -770,6 +816,12 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -820,6 +872,12 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -884,6 +942,12 @@
         <is>
           <t>2026-03-02, 2026-03-09</t>
         </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -922,6 +986,12 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -971,6 +1041,12 @@
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1016,6 +1092,12 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1061,6 +1143,12 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1090,6 +1178,12 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1127,6 +1221,12 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1176,6 +1276,12 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1245,6 +1351,12 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1305,6 +1417,12 @@
         <is>
           <t>2026-03-06</t>
         </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1335,6 +1453,12 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1368,6 +1492,12 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1433,6 +1563,12 @@
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1462,6 +1598,12 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1491,6 +1633,12 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1559,6 +1707,12 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1609,6 +1763,12 @@
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1646,6 +1806,12 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1691,6 +1857,12 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1720,6 +1892,12 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1788,6 +1966,12 @@
         <is>
           <t>2026-03-10</t>
         </is>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1818,6 +2002,12 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1875,6 +2065,12 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1943,6 +2139,12 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1981,6 +2183,12 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2049,6 +2257,12 @@
         <is>
           <t>2026-03-04</t>
         </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2099,6 +2313,12 @@
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2136,6 +2356,12 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2204,6 +2430,12 @@
         <is>
           <t>2026-03-05</t>
         </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2234,6 +2466,12 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2299,6 +2537,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2367,6 +2611,12 @@
         <is>
           <t>2026-03-07</t>
         </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2417,6 +2667,12 @@
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +500,16 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>CumplimientoIntermedia</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>CumplimientoSemanal</t>
         </is>
       </c>
     </row>
@@ -545,6 +555,12 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -580,6 +596,12 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,6 +637,12 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -668,6 +696,12 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -713,6 +747,12 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -748,6 +788,12 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -822,6 +868,12 @@
       </c>
       <c r="Q8" t="n">
         <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -878,6 +930,12 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -948,6 +1006,12 @@
       </c>
       <c r="Q10" t="n">
         <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
@@ -992,6 +1056,12 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1047,6 +1117,12 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="R12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1098,6 +1174,12 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1147,6 +1229,12 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1184,6 +1272,12 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1227,6 +1321,12 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1282,6 +1382,12 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1357,6 +1463,12 @@
       <c r="Q18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1423,6 +1535,12 @@
       </c>
       <c r="Q19" t="n">
         <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1459,6 +1577,12 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1498,6 +1622,12 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1567,6 +1697,12 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1604,6 +1740,12 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1639,6 +1781,12 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1713,6 +1861,12 @@
       </c>
       <c r="Q25" t="n">
         <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="26">
@@ -1767,6 +1921,12 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1812,6 +1972,12 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1861,6 +2027,12 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1898,6 +2070,12 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1972,6 +2150,12 @@
       </c>
       <c r="Q30" t="n">
         <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="31">
@@ -2008,6 +2192,12 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2071,6 +2261,12 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2145,6 +2341,12 @@
       </c>
       <c r="Q33" t="n">
         <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="34">
@@ -2189,6 +2391,12 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2263,6 +2471,12 @@
       </c>
       <c r="Q35" t="n">
         <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -2317,6 +2531,12 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2362,6 +2582,12 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2436,6 +2662,12 @@
       </c>
       <c r="Q38" t="n">
         <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="39">
@@ -2472,6 +2704,12 @@
       <c r="Q39" t="n">
         <v>0</v>
       </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2543,6 +2781,12 @@
       <c r="Q40" t="n">
         <v>1</v>
       </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2617,6 +2861,12 @@
       </c>
       <c r="Q41" t="n">
         <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="42">
@@ -2673,6 +2923,12 @@
       <c r="Q42" t="n">
         <v>0</v>
       </c>
+      <c r="R42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,12 +539,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -586,8 +586,16 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-11</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
@@ -627,7 +635,11 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -666,40 +678,40 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -731,12 +743,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -829,51 +841,51 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-19</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -890,7 +902,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -898,43 +910,59 @@
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-27</t>
+        </is>
+      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -971,47 +999,51 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-04, 2026-03-04, 2026-03-07</t>
+          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-04, 2026-03-04, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-17</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1040,14 +1072,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
@@ -1085,7 +1113,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1097,28 +1125,28 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.25</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1146,7 +1174,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1158,24 +1186,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1195,47 +1227,63 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SABADO</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="J14" t="n">
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>2026-02-26, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -1305,12 +1353,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-04, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-04, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1354,7 +1402,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1366,24 +1414,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1423,12 +1475,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1439,35 +1491,35 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1496,12 +1548,12 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1512,35 +1564,35 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="S19" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -1608,12 +1660,12 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
@@ -1663,12 +1715,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1679,31 +1731,35 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-16, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-20</t>
+        </is>
+      </c>
       <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.25</v>
-      </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
@@ -1730,7 +1786,11 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1771,7 +1831,11 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1789,85 +1853,41 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1877,7 +1897,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1886,48 +1906,68 @@
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="J26" t="n">
         <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-04, 2026-03-06</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.25</v>
-      </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1938,30 +1978,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-10</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -1987,38 +2035,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2044,34 +2084,58 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2085,77 +2149,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2166,93 +2190,109 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>PEÑON DE ALICANTE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PRUEBA</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
@@ -2276,18 +2316,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2297,17 +2337,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2316,37 +2356,21 @@
       <c r="K33" t="n">
         <v>4</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2357,45 +2381,77 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2406,77 +2462,45 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2487,57 +2511,77 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
       <c r="J36" t="n">
         <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>2026-02-11, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
       <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S36" t="n">
         <v>0.25</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2548,42 +2592,58 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -2597,77 +2657,45 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2678,37 +2706,77 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2719,73 +2787,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-05</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2796,7 +2828,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2807,27 +2839,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2838,35 +2870,35 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-06, 2026-02-26</t>
         </is>
       </c>
       <c r="P41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.25</v>
-      </c>
       <c r="S41" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -2877,7 +2909,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2886,47 +2918,128 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="J42" t="n">
         <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
       <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S42" t="n">
+      <c r="S43" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,80 +434,85 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>CLUSTER</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fechas_Intermedia</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Fechas_Semanal</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Coincidencias_Intermedia</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Coincidencias_Semanal</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -531,27 +536,25 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -559,6 +562,9 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -580,27 +586,25 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -608,6 +612,9 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -629,23 +636,21 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -653,6 +658,9 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -668,52 +676,53 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -735,27 +744,25 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
@@ -763,6 +770,9 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -784,19 +794,17 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
@@ -804,6 +812,9 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,74 +830,75 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-19</t>
         </is>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>0.5</v>
       </c>
+      <c r="T8" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,68 +912,69 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-27</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -977,72 +990,73 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-17</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
       <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1064,23 +1078,21 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
@@ -1088,6 +1100,9 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1103,52 +1118,53 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>4</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1164,52 +1180,53 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
         <v>3</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>0.75</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1225,64 +1242,65 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.25</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1304,19 +1322,17 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
@@ -1324,6 +1340,9 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1345,27 +1364,25 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
@@ -1373,6 +1390,9 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1388,56 +1408,57 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>0.25</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1453,74 +1474,75 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
       <c r="K18" t="n">
         <v>4</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>4</v>
-      </c>
       <c r="Q18" t="n">
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1534,64 +1556,65 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>2</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>0.75</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1613,19 +1636,17 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
@@ -1633,6 +1654,9 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1654,23 +1678,21 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
@@ -1678,6 +1700,9 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1693,72 +1718,73 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
       <c r="K22" t="n">
         <v>4</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-16, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-20</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>4</v>
-      </c>
       <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1780,23 +1806,21 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
@@ -1804,6 +1828,9 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1825,23 +1852,21 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
@@ -1849,6 +1874,9 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,26 +1896,27 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
       <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1901,74 +1930,75 @@
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>4</v>
-      </c>
       <c r="K26" t="n">
         <v>4</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="P26" t="n">
-        <v>4</v>
-      </c>
       <c r="Q26" t="n">
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1982,41 +2012,39 @@
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>4</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
@@ -2024,6 +2052,9 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2045,27 +2076,25 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
@@ -2073,6 +2102,9 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2088,56 +2120,57 @@
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>4</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
         <v>3</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.75</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2159,19 +2192,17 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
@@ -2179,6 +2210,9 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2194,72 +2228,73 @@
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>4</v>
-      </c>
       <c r="K31" t="n">
         <v>4</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="P31" t="n">
-        <v>4</v>
-      </c>
       <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
         <v>3</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -2281,23 +2316,21 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
@@ -2305,6 +2338,9 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2320,49 +2356,47 @@
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>4</v>
-      </c>
       <c r="K33" t="n">
         <v>4</v>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>4</v>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
@@ -2370,6 +2404,9 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2385,72 +2422,73 @@
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>4</v>
-      </c>
       <c r="K34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="P34" t="n">
-        <v>4</v>
-      </c>
       <c r="Q34" t="n">
         <v>4</v>
       </c>
       <c r="R34" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2472,27 +2510,25 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -2500,6 +2536,9 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2515,72 +2554,73 @@
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>4</v>
-      </c>
       <c r="K36" t="n">
         <v>4</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-02-11, 2026-02-24</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>1</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>0.5</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -2596,56 +2636,57 @@
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>4</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-12, 2026-02-25</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
         <v>3</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>0.75</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2667,27 +2708,25 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -2695,6 +2734,9 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2710,72 +2752,73 @@
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>4</v>
-      </c>
       <c r="K39" t="n">
         <v>4</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="P39" t="n">
-        <v>4</v>
-      </c>
       <c r="Q39" t="n">
         <v>4</v>
       </c>
       <c r="R39" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" t="n">
         <v>1</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2797,19 +2840,17 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -2817,6 +2858,9 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2832,72 +2876,73 @@
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>09:00:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>4</v>
-      </c>
       <c r="K41" t="n">
         <v>4</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-16, 2026-02-26</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-26</t>
         </is>
       </c>
-      <c r="P41" t="n">
-        <v>4</v>
-      </c>
       <c r="Q41" t="n">
+        <v>4</v>
+      </c>
+      <c r="R41" t="n">
         <v>2</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2913,74 +2958,75 @@
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>4</v>
-      </c>
       <c r="K42" t="n">
         <v>4</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
         <v>0.75</v>
       </c>
+      <c r="T42" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2994,52 +3040,53 @@
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>4</v>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
-        <v>4</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,85 +434,90 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CLUSTER</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Fechas_Intermedia</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Fechas_Semanal</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Coincidencias_Intermedia</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Coincidencias_Semanal</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -537,27 +542,25 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -565,6 +568,9 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -587,27 +593,25 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -615,6 +619,9 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -637,23 +644,21 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -661,6 +666,9 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -679,50 +687,55 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -745,27 +758,25 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -773,6 +784,9 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,19 +809,17 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -815,6 +827,9 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,70 +848,75 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
       <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-19</t>
         </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>0.5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -915,66 +935,71 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
       <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-27</t>
         </is>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
       <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -993,70 +1018,75 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-17</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
       <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1079,23 +1109,21 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -1103,6 +1131,9 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1121,50 +1152,55 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>4</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1183,50 +1219,55 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.75</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1245,62 +1286,67 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
       <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
         <v>0.25</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1323,19 +1369,17 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -1343,6 +1387,9 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1365,27 +1412,25 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -1393,6 +1438,9 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1411,54 +1459,59 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.25</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1477,70 +1530,75 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
+          <t>LA SCALA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
       <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
       <c r="R18" t="n">
         <v>4</v>
       </c>
       <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1559,62 +1617,67 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
       <c r="L19" t="n">
         <v>4</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>3</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>0.75</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1637,19 +1700,17 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -1657,6 +1718,9 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1679,23 +1743,21 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -1703,6 +1765,9 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1721,70 +1786,75 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>4</v>
-      </c>
       <c r="L22" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-16, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-20</t>
         </is>
       </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
       <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1807,23 +1877,21 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -1831,6 +1899,9 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1853,23 +1924,21 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -1877,6 +1946,9 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1897,26 +1969,27 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1933,70 +2006,75 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>4</v>
-      </c>
       <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
       <c r="R26" t="n">
         <v>4</v>
       </c>
       <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2015,39 +2093,41 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>4</v>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -2055,6 +2135,9 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2077,27 +2160,25 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>0</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -2105,6 +2186,9 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2123,54 +2207,59 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
         <v>3</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
       <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>0.75</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2193,19 +2282,17 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -2213,6 +2300,9 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2231,70 +2321,75 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>4</v>
-      </c>
       <c r="L31" t="n">
         <v>4</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="Q31" t="n">
-        <v>4</v>
-      </c>
       <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
         <v>3</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -2317,23 +2412,21 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -2341,6 +2434,9 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2357,49 +2453,47 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>4</v>
-      </c>
       <c r="L33" t="n">
         <v>4</v>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>4</v>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -2407,6 +2501,9 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2425,70 +2522,75 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>4</v>
-      </c>
       <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
       <c r="R34" t="n">
         <v>4</v>
       </c>
       <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2511,27 +2613,25 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -2539,6 +2639,9 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2557,70 +2660,75 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>4</v>
-      </c>
       <c r="L36" t="n">
         <v>4</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>2026-02-11, 2026-02-24</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>2</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.5</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -2639,54 +2747,59 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>4</v>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-12, 2026-02-25</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
         <v>3</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
       <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>0.75</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2709,27 +2822,25 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>0</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -2737,6 +2848,9 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2755,70 +2869,75 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>4</v>
-      </c>
       <c r="L39" t="n">
         <v>4</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="n">
+        <v>4</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="Q39" t="n">
-        <v>4</v>
-      </c>
       <c r="R39" t="n">
         <v>4</v>
       </c>
       <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="n">
         <v>1</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2841,19 +2960,17 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>0</v>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -2861,6 +2978,9 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2879,70 +2999,75 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>09:00:00</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>4</v>
-      </c>
       <c r="L41" t="n">
         <v>4</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="n">
+        <v>4</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-16, 2026-02-26</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-26</t>
         </is>
       </c>
-      <c r="Q41" t="n">
-        <v>4</v>
-      </c>
       <c r="R41" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" t="n">
         <v>2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>1</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2961,70 +3086,75 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>4</v>
-      </c>
       <c r="L42" t="n">
         <v>4</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>3</v>
       </c>
       <c r="R42" t="n">
         <v>3</v>
       </c>
       <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
         <v>0.75</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -3043,50 +3173,55 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>4</v>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
-        <v>4</v>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,95 +429,110 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Director de obra</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ValidacionParametrización</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Fechas_Intermedia</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Fechas_Semanal</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Coincidencias_Intermedia</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Coincidencias_Semanal</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -534,43 +549,54 @@
           <t>ABADIA SAN RAFAEL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -585,43 +611,54 @@
           <t>ARAGON</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -636,39 +673,50 @@
           <t>BAVIERA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,60 +731,87 @@
           <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fabian Enrique Gutierrez Tole</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
+      <c r="X5" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -750,43 +825,54 @@
           <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -801,35 +887,46 @@
           <t>CADIZ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,79 +941,94 @@
           <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Licette Tatiana Koop Santa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-19</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>0.5</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -931,75 +1043,92 @@
           <t>EL CAMPO</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Ardila Castañeda</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>TRES QUEBRADAS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-27</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1014,79 +1143,94 @@
           <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Doriam Mayreth Sanchez Saenz</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>IBERIA</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-09, 2026-02-17</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1101,39 +1245,50 @@
           <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1148,60 +1303,87 @@
           <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Maicol David Sanchez Ortiz</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>ZENTRAL</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
-        <v>4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -1215,60 +1397,87 @@
           <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nidia Esperanza Herrera Padilla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>ALSACIA RESERVADO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
         <v>3</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.75</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
+      <c r="X13" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
@@ -1282,71 +1491,86 @@
           <t>LA CABRERA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>Martin Rafael Bohorquez Marrugo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>0.25</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1361,35 +1585,46 @@
           <t>LA CRUZ</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1404,43 +1639,54 @@
           <t>LA PALMA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1455,64 +1701,91 @@
           <t>LA PEÑA</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jose Alejandro Barcenas Moreno</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>TRES QUEBRADAS</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" t="n">
         <v>0.25</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
+      <c r="X17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1526,79 +1799,94 @@
           <t>LA SCALA</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Javier Manuel Gonzalez Angulo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>LA SCALA</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4</v>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1613,71 +1901,86 @@
           <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALSACIA RESERVADO</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>Nidia Esperanza Herrera Padilla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>0.75</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1692,35 +1995,46 @@
           <t>LINZ E1</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1735,39 +2049,50 @@
           <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1782,79 +2107,94 @@
           <t>LORCA</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Johanna Diaz Mora</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>IBERIA</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-16, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-20</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>4</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
         <v>2</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1869,39 +2209,50 @@
           <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1916,39 +2267,50 @@
           <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1970,26 +2332,29 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>2026-02-25, 2026-02-25</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2002,79 +2367,94 @@
           <t>METROPOLI 30</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Yorleynis Montejo Ruiz</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>METROPOLI 30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4</v>
+      </c>
+      <c r="W26" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2089,56 +2469,87 @@
           <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Juan Alberto Gutierrez Forero</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -2152,43 +2563,54 @@
           <t>PASEO DE SEVILLA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2203,64 +2625,91 @@
           <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>ZIPAQUIRA</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>4</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-11, 2026-02-18</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
+        <v>3</v>
+      </c>
+      <c r="W29" t="n">
         <v>0.75</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
+      <c r="X29" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="30">
@@ -2274,35 +2723,46 @@
           <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2317,79 +2777,94 @@
           <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>IBERIA</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4</v>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>4</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
+        <v>4</v>
+      </c>
+      <c r="V31" t="n">
         <v>3</v>
       </c>
-      <c r="T31" t="n">
+      <c r="W31" t="n">
         <v>1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -2404,39 +2879,50 @@
           <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2448,63 +2934,98 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>4</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2515,83 +3036,58 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>SAN LUCAS LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2602,47 +3098,98 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>SAN MATEO - LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026-02-11, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -2653,83 +3200,94 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>SAN SEBASTIAN LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>ZIPAQUIRA</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>4</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4</v>
-      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-02-11, 2026-02-24</t>
-        </is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>2</v>
-      </c>
-      <c r="S36" t="n">
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X36" t="n">
         <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="37">
@@ -2740,66 +3298,57 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>4</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
-        <v>3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2811,47 +3360,100 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2862,83 +3464,50 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>4</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2949,39 +3518,98 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mauricio Andres Cervantes</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-26</t>
+        </is>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
@@ -2992,83 +3620,98 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>4</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4</v>
-      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>4</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R41" t="n">
-        <v>4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
       </c>
       <c r="U41" t="n">
-        <v>0.5</v>
+        <v>3</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="42">
@@ -3079,150 +3722,90 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>4</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
-        </is>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
-        <v>3</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.75</v>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-02-13, 2026-02-27</t>
+        </is>
       </c>
       <c r="U42" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ZURI - ZENTRAL</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>ZENTRAL</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>4</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="n">
-        <v>4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>2</v>
+      </c>
+      <c r="W42" t="n">
         <v>1</v>
       </c>
-      <c r="U43" t="n">
-        <v>0</v>
+      <c r="X42" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2315,36 +2315,48 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>MALAGA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-02-25, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
@@ -2353,110 +2365,54 @@
       <c r="V25" t="n">
         <v>0</v>
       </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
+          <t>MALAGA CASTILLA RESERVADO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Yorleynis Montejo Ruiz</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>METROPOLI 30</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>4</v>
-      </c>
-      <c r="P26" t="n">
-        <v>4</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2466,7 +2422,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2482,37 +2438,45 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Juan Alberto Gutierrez Forero</t>
+          <t>Yorleynis Montejo Ruiz</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
       <c r="O27" t="n">
         <v>4</v>
       </c>
@@ -2521,35 +2485,35 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
+        <v>4</v>
+      </c>
+      <c r="W27" t="n">
         <v>1</v>
       </c>
-      <c r="W27" t="n">
-        <v>0.75</v>
-      </c>
       <c r="X27" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2560,58 +2524,90 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Juan Alberto Gutierrez Forero</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="29">
@@ -2622,12 +2618,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2636,80 +2632,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
+          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2720,12 +2680,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2734,36 +2694,80 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
@@ -2774,12 +2778,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2788,84 +2792,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Jennifer Paola Lopez Vaca</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2876,54 +2832,98 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2948,84 +2948,40 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Jhon Alexander Guarin Reina</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3036,58 +2992,98 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3098,12 +3094,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3112,84 +3108,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2026-02-11, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3200,7 +3156,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3216,7 +3172,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
+          <t>Zuri Andreina Orduz Sepulveda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3227,30 +3183,34 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
       <c r="O36" t="n">
         <v>4</v>
       </c>
@@ -3259,35 +3219,35 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+          <t>2026-02-11, 2026-02-24</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="37">
@@ -3298,12 +3258,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3312,44 +3272,80 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3360,100 +3356,58 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3464,50 +3418,100 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3518,12 +3522,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3532,84 +3536,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Mauricio Andres Cervantes</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3620,7 +3576,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3636,13 +3592,13 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Mauricio Andres Cervantes</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3652,17 +3608,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3672,7 +3628,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3683,35 +3639,35 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-26</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -3722,7 +3678,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3733,78 +3689,180 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yenny Paola Munevar Peña</t>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>ZENTRAL</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="O42" t="n">
-        <v>4</v>
-      </c>
-      <c r="P42" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q42" t="inlineStr">
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>2026-02-13, 2026-02-27</t>
         </is>
       </c>
-      <c r="U42" t="n">
-        <v>4</v>
-      </c>
-      <c r="V42" t="n">
+      <c r="U43" t="n">
+        <v>4</v>
+      </c>
+      <c r="V43" t="n">
         <v>2</v>
       </c>
-      <c r="W42" t="n">
+      <c r="W43" t="n">
         <v>1</v>
       </c>
-      <c r="X42" t="n">
+      <c r="X43" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -1717,7 +1717,9 @@
           <t>Jose Alejandro Barcenas Moreno</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>TRES QUEBRADAS</t>
@@ -1725,7 +1727,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1738,10 +1740,14 @@
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MALAGA</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2361,8 +2361,16 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-02-25, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
@@ -2379,46 +2387,106 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Yorleynis Montejo Ruiz</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-02-25, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2428,7 +2496,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2444,43 +2512,35 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yorleynis Montejo Ruiz</t>
+          <t>Juan Alberto Gutierrez Forero</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2491,35 +2551,35 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -2530,90 +2590,58 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Juan Alberto Gutierrez Forero</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
+          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2624,12 +2652,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2638,44 +2666,80 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30">
@@ -2686,12 +2750,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2700,80 +2764,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2784,12 +2804,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2798,36 +2818,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32">
@@ -2838,98 +2906,54 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Jennifer Paola Lopez Vaca</t>
-        </is>
-      </c>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2940,12 +2964,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2954,40 +2978,84 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2998,98 +3066,58 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Jhon Alexander Guarin Reina</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3100,12 +3128,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3114,44 +3142,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026-02-11, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -3162,7 +3230,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3178,7 +3246,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
+          <t>Yuli Maribel Arias Cifuentes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3189,32 +3257,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3225,35 +3289,35 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-02-11, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X36" t="n">
         <v>1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="37">
@@ -3264,12 +3328,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3278,80 +3342,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3362,58 +3390,100 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3424,100 +3494,50 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3528,12 +3548,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3542,36 +3562,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mauricio Andres Cervantes</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
@@ -3582,7 +3650,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3598,13 +3666,13 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mauricio Andres Cervantes</t>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>NORTE</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3614,17 +3682,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3634,7 +3702,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3645,35 +3713,35 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-26</t>
+          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X41" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="42">
@@ -3684,7 +3752,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>ZURI - ZENTRAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3695,18 +3763,18 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Yenny Paola Munevar Peña</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>ZENTRAL</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3714,21 +3782,13 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
@@ -3747,128 +3807,34 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-13, 2026-02-27</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ZURI - ZENTRAL</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Yenny Paola Munevar Peña</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>ZENTRAL</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-02-13, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="U43" t="n">
-        <v>4</v>
-      </c>
-      <c r="V43" t="n">
-        <v>2</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1</v>
-      </c>
-      <c r="X43" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -1518,7 +1518,11 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>VIERNES</t>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -758,13 +758,21 @@
           <t>LUNES</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
@@ -772,7 +780,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -798,7 +806,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="U5" t="n">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -861,12 +861,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-16, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-02-25, 2026-02-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-24</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X5" t="n">
         <v>0.75</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1226,20 +1226,20 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-17</t>
+          <t>2026-02-02, 2026-02-17</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2987,87 +2987,55 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Jhon Alexander Guarin Reina</t>
-        </is>
-      </c>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-07, 2026-02-10, 2026-02-14, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3078,58 +3046,98 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3140,12 +3148,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3154,84 +3162,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2026-02-11, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3242,7 +3210,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3258,7 +3226,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
+          <t>Zuri Andreina Orduz Sepulveda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3269,30 +3237,34 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
       <c r="O36" t="n">
         <v>4</v>
       </c>
@@ -3301,35 +3273,35 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+          <t>2026-02-11, 2026-02-24</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="37">
@@ -3340,12 +3312,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3354,44 +3326,80 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3402,100 +3410,58 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3506,50 +3472,100 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3560,12 +3576,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3574,84 +3590,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Mauricio Andres Cervantes</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3662,7 +3630,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3678,13 +3646,13 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Mauricio Andres Cervantes</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3694,17 +3662,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3714,7 +3682,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3725,35 +3693,35 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-26</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -3764,7 +3732,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3775,78 +3743,180 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yenny Paola Munevar Peña</t>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>ZENTRAL</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="O42" t="n">
-        <v>4</v>
-      </c>
-      <c r="P42" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q42" t="inlineStr">
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>2026-02-13, 2026-02-27</t>
         </is>
       </c>
-      <c r="U42" t="n">
-        <v>4</v>
-      </c>
-      <c r="V42" t="n">
+      <c r="U43" t="n">
+        <v>4</v>
+      </c>
+      <c r="V43" t="n">
         <v>2</v>
       </c>
-      <c r="W42" t="n">
+      <c r="W43" t="n">
         <v>1</v>
       </c>
-      <c r="X42" t="n">
+      <c r="X43" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2026-03-03, 2026-03-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -637,16 +637,8 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
@@ -699,11 +691,7 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -775,51 +763,51 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="X5" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -861,12 +849,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -993,51 +981,51 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-19</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -1097,12 +1085,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1113,31 +1101,31 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-02-12, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1195,51 +1183,47 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-07</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-03-02, 2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-17</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
@@ -1281,10 +1265,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
@@ -1347,12 +1335,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1363,32 +1351,32 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X12" t="n">
         <v>0.25</v>
@@ -1432,21 +1420,29 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1457,35 +1453,27 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1539,12 +1527,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1555,35 +1543,31 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-28</t>
+          <t>2026-03-03, 2026-03-05</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-02-26, 2026-02-28</t>
+          <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1679,12 +1663,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1759,12 +1743,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1775,35 +1759,31 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0.25</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1861,12 +1841,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1877,35 +1857,35 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1946,21 +1926,29 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1971,35 +1959,35 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-02-20, 2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -2093,12 +2081,12 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
@@ -2169,12 +2157,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2185,35 +2173,31 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-20</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2253,11 +2237,7 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2311,11 +2291,7 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2373,16 +2349,8 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
@@ -2453,12 +2421,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2469,35 +2437,35 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -2547,12 +2515,12 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2563,32 +2531,28 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-03-04, 2026-03-06</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0.25</v>
@@ -2633,12 +2597,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+          <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
+          <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -2707,12 +2671,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -2721,37 +2685,25 @@
       <c r="P29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2863,51 +2815,51 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P31" t="n">
         <v>4</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-10</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="X31" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="32">
@@ -2947,11 +2899,7 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3007,22 +2955,30 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-10, 2026-02-14, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-28</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
@@ -3093,12 +3049,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3109,35 +3065,35 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="35">
@@ -3179,12 +3135,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3257,12 +3213,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3273,32 +3229,32 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-02-11, 2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X36" t="n">
         <v>0.25</v>
@@ -3355,12 +3311,12 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3371,35 +3327,27 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3441,12 +3389,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -3521,12 +3469,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -3537,35 +3485,35 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="40">
@@ -3677,12 +3625,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3693,35 +3641,31 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-03-02, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="42">
@@ -3779,12 +3723,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3795,35 +3739,35 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X42" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="43">
@@ -3873,12 +3817,12 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -3889,35 +3833,35 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-02-13, 2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X43" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2997,12 +2997,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PRUEBA BARRANQUILLA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3013,87 +3013,63 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Jhon Alexander Guarin Reina</t>
-        </is>
-      </c>
+          <t>Ramiro Gonzalez</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
         <v>4</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3104,58 +3080,98 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -3166,12 +3182,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3180,84 +3196,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+          <t>2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3268,7 +3244,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3284,7 +3260,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
+          <t>Zuri Andreina Orduz Sepulveda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3295,30 +3271,34 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
       <c r="O37" t="n">
         <v>4</v>
       </c>
@@ -3327,27 +3307,35 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="n">
         <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
         <v>0.25</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="38">
@@ -3358,12 +3346,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3372,41 +3360,69 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3420,100 +3436,58 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3524,50 +3498,100 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="41">
@@ -3578,12 +3602,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3592,80 +3616,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Mauricio Andres Cervantes</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-05</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3676,7 +3656,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3692,13 +3672,13 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Mauricio Andres Cervantes</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3708,17 +3688,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3728,7 +3708,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3739,32 +3719,28 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0.25</v>
@@ -3778,7 +3754,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3789,18 +3765,18 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yenny Paola Munevar Peña</t>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ZENTRAL</t>
+          <t>NORTE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3808,13 +3784,21 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
@@ -3838,7 +3822,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -3848,7 +3832,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="U43" t="n">
@@ -3861,6 +3845,100 @@
         <v>0.25</v>
       </c>
       <c r="X43" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X44" t="n">
         <v>0.25</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -3053,20 +3053,24 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -3013,7 +3013,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ramiro Gonzalez</t>
+          <t>Juan Vargas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -3020,7 +3020,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -3025,28 +3025,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
         <v>4</v>
@@ -3057,20 +3057,16 @@
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -637,8 +637,16 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
@@ -691,7 +699,11 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -763,51 +775,51 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
         <v>1</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.4</v>
-      </c>
       <c r="X5" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -849,12 +861,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -981,51 +993,51 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-19</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -1085,12 +1097,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1101,31 +1113,31 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -1183,47 +1195,51 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-07</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-17</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1265,14 +1281,10 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
@@ -1335,12 +1347,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1351,32 +1363,32 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
         <v>0.25</v>
@@ -1437,12 +1449,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1453,27 +1465,35 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
@@ -1527,12 +1547,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1543,31 +1563,35 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
       <c r="U14" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
         <v>0.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -1663,12 +1687,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1743,12 +1767,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1759,31 +1783,35 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
         <v>0.25</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1841,12 +1869,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1857,35 +1885,35 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
         <v>1</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1943,12 +1971,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1959,35 +1987,35 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -2081,12 +2109,12 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
@@ -2157,12 +2185,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2173,31 +2201,35 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-20</t>
+        </is>
+      </c>
       <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" t="n">
         <v>1</v>
       </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
@@ -2237,7 +2269,11 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2291,7 +2327,11 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2349,8 +2389,16 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
@@ -2421,12 +2469,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2437,35 +2485,35 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4</v>
+      </c>
+      <c r="W26" t="n">
         <v>1</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -2515,12 +2563,12 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2531,28 +2579,32 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-06</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X27" t="n">
         <v>0.25</v>
@@ -2597,12 +2649,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -2671,12 +2723,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -2685,25 +2737,37 @@
       <c r="P29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30">
@@ -2815,51 +2879,51 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
         <v>4</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-10</t>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
+        <v>3</v>
+      </c>
+      <c r="W31" t="n">
         <v>1</v>
       </c>
-      <c r="W31" t="n">
-        <v>0.4</v>
-      </c>
       <c r="X31" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32">
@@ -2899,7 +2963,11 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -2955,30 +3023,22 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28, 2026-03-30</t>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
@@ -3016,7 +3076,11 @@
           <t>Juan Vargas</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ju</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
@@ -3037,12 +3101,12 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3051,11 +3115,7 @@
       <c r="P34" t="n">
         <v>4</v>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -3127,12 +3187,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -3143,35 +3203,35 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="U35" t="n">
+        <v>4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4</v>
+      </c>
+      <c r="W35" t="n">
         <v>1</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -3213,12 +3273,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3291,12 +3351,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3307,32 +3367,32 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-11, 2026-02-24</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="X37" t="n">
         <v>0.25</v>
@@ -3389,12 +3449,12 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -3405,27 +3465,35 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X38" t="n">
         <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3467,12 +3535,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -3547,12 +3615,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -3563,35 +3631,35 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="U40" t="n">
+        <v>4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4</v>
+      </c>
+      <c r="W40" t="n">
         <v>1</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="41">
@@ -3703,12 +3771,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3719,31 +3787,35 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-26</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
+        <v>2</v>
+      </c>
+      <c r="W42" t="n">
         <v>1</v>
       </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
       <c r="X42" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43">
@@ -3801,12 +3873,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -3817,35 +3889,35 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="X43" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
@@ -3895,12 +3967,12 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -3911,35 +3983,35 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-13, 2026-02-27</t>
         </is>
       </c>
       <c r="U44" t="n">
+        <v>4</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2</v>
+      </c>
+      <c r="W44" t="n">
         <v>1</v>
       </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X44" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,16 +575,8 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
@@ -603,63 +595,91 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Abimael Padilla</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
+          <t>2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+          <t>2025-11-08, 2025-11-14, 2025-11-25, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2025-11-08, 2025-11-14, 2025-11-28</t>
+        </is>
+      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
@@ -670,7 +690,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAVIERA</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -681,7 +701,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -699,11 +719,7 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -728,12 +744,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>BAVIERA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -742,84 +758,36 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fabian Enrique Gutierrez Tole</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -830,58 +798,98 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BURGOS CASTILLA RESERVADO</t>
+          <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fabian Enrique Gutierrez Tole</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+        </is>
+      </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+          <t>2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-12, 2025-11-26</t>
+        </is>
+      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -892,7 +900,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CADIZ</t>
+          <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -946,98 +954,58 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>CADIZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Licette Tatiana Koop Santa</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-10</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-19</t>
-        </is>
-      </c>
+          <t>2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1048,7 +1016,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1059,50 +1027,48 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Juan Sebastian Ardila Castañeda</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
+          <t>Licette Tatiana Koop Santa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1113,28 +1079,32 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
+          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2025-11-10, 2025-11-24</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-19</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X9" t="n">
         <v>0.5</v>
@@ -1148,7 +1118,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1164,43 +1134,45 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doriam Mayreth Sanchez Saenz</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Juan Sebastian Ardila Castañeda</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1211,35 +1183,31 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+          <t>2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-17</t>
-        </is>
-      </c>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1250,54 +1218,94 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Doriam Mayreth Sanchez Saenz</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+        </is>
+      </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2025-11-11, 2025-11-25</t>
+        </is>
+      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -1308,12 +1316,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1322,76 +1330,44 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Maicol David Sanchez Ortiz</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ZENTRAL</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-10, 2025-11-14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
+          <t>2025-11-10, 2025-11-14</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1402,7 +1378,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1418,43 +1394,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nidia Esperanza Herrera Padilla</t>
+          <t>Maicol David Sanchez Ortiz</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ALSACIA RESERVADO</t>
+          <t>ZENTRAL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1465,35 +1433,31 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X13" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1504,7 +1468,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1515,18 +1479,18 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Martin Rafael Bohorquez Marrugo</t>
+          <t>Nidia Esperanza Herrera Padilla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1534,11 +1498,7 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>VIERNES</t>
@@ -1547,12 +1507,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1563,35 +1523,31 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-28</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-02-26, 2026-02-28</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
+        <v>4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1</v>
       </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1602,12 +1558,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA CRUZ</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1616,36 +1572,76 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Martin Rafael Bohorquez Marrugo</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
+        </is>
+      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1656,7 +1652,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA CRUZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1687,12 +1683,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2025-11-13, 2025-11-21</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1718,12 +1714,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1732,86 +1728,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Jose Alejandro Barcenas Moreno</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1822,7 +1776,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1838,13 +1792,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Javier Manuel Gonzalez Angulo</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Jose Alejandro Barcenas Moreno</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1854,27 +1810,27 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1885,35 +1841,35 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-07, 2025-11-14, 2025-11-19, 2025-11-26</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-07, 2025-11-18, 2025-11-21, 2025-11-28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-19, 2025-11-26</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-07, 2025-11-21, 2025-11-28</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="19">
@@ -1924,7 +1880,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1935,48 +1891,48 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nidia Esperanza Herrera Padilla</t>
+          <t>Javier Manuel Gonzalez Angulo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ALSACIA RESERVADO</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1987,35 +1943,35 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-12, 2025-11-20</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-02-20, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-12, 2025-11-20</t>
         </is>
       </c>
       <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" t="n">
         <v>3</v>
       </c>
-      <c r="V19" t="n">
-        <v>2</v>
-      </c>
       <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
         <v>0.75</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -2026,12 +1982,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LINZ E1</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2040,33 +1996,69 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nidia Esperanza Herrera Padilla</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2080,7 +2072,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>LINZ E1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2109,11 +2101,7 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2138,98 +2126,58 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Johanna Diaz Mora</t>
-        </is>
-      </c>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-20</t>
-        </is>
-      </c>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2240,54 +2188,98 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LYON 2 CIUDAD LA SALLE</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Johanna Diaz Mora</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+          <t>2025-11-04, 2025-11-17, 2025-11-19, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-17, 2025-11-20</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2025-11-19, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="24">
@@ -2298,7 +2290,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LYON CIUDAD LA SALLE</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2327,11 +2319,7 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2356,7 +2344,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
+          <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2367,16 +2355,12 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -2389,16 +2373,8 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
@@ -2422,98 +2398,54 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Yorleynis Montejo Ruiz</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2524,7 +2456,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2540,35 +2472,43 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Juan Alberto Gutierrez Forero</t>
+          <t>Yorleynis Montejo Ruiz</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2579,35 +2519,35 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+          <t>2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
+        <v>4</v>
+      </c>
+      <c r="W27" t="n">
         <v>1</v>
       </c>
-      <c r="W27" t="n">
-        <v>0.75</v>
-      </c>
       <c r="X27" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2618,58 +2558,90 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Juan Alberto Gutierrez Forero</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+          <t>2025-11-11, 2025-11-14, 2025-11-18, 2025-11-21, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2025-11-21, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2025-11-14, 2025-11-21, 2025-11-28</t>
+        </is>
+      </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="29">
@@ -2680,12 +2652,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2694,80 +2666,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
+          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2778,12 +2714,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2792,36 +2728,80 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-14, 2025-11-28</t>
+        </is>
+      </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
@@ -2832,12 +2812,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2846,84 +2826,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Jennifer Paola Lopez Vaca</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
+          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2934,54 +2874,98 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
@@ -2992,50 +2976,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>SABADO</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -3057,12 +3025,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PRUEBA BARRANQUILLA</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3073,40 +3041,32 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juan Vargas</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Ju</t>
-        </is>
-      </c>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>SUR</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>SABADO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-01, 2025-11-03, 2025-11-08, 2025-11-10, 2025-11-15, 2025-11-17, 2025-11-22, 2025-11-24, 2025-11-29</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3135,12 +3095,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3151,48 +3111,48 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jhon Alexander Guarin Reina</t>
+          <t>Kelly Gutierrez</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
+          <t>PUERTA DORADA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -3203,97 +3163,133 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-27</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-08, 2025-11-28</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Orlando Iguaran</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+        </is>
+      </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="37">
@@ -3304,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3315,18 +3311,18 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
+          <t>Jhon Alexander Guarin Reina</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ZIPAQUIRA</t>
+          <t>CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3336,27 +3332,27 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3367,35 +3363,35 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-02-11, 2026-02-24</t>
+          <t>2025-11-12, 2025-11-26</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
         <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3406,12 +3402,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3420,80 +3416,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3504,12 +3456,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3518,41 +3470,77 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+        </is>
+      </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3566,7 +3554,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3577,20 +3565,18 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
+          <t>ZIPAQUIRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3605,22 +3591,18 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -3629,37 +3611,21 @@
       <c r="P40" t="n">
         <v>4</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3670,7 +3636,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3699,8 +3665,16 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
@@ -3724,7 +3698,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3735,35 +3709,37 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mauricio Andres Cervantes</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>14:00:00</t>
@@ -3771,12 +3747,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3787,35 +3763,35 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-12, 2025-11-19, 2025-11-27</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-26</t>
+          <t>2025-11-13, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X42" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="43">
@@ -3826,12 +3802,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -3840,84 +3816,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3928,7 +3856,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3939,79 +3867,279 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yenny Paola Munevar Peña</t>
+          <t>Mauricio Andres Cervantes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-14, 2025-11-21</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>3</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-14, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
+      </c>
+      <c r="V45" t="n">
+        <v>3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>ZENTRAL</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>4</v>
-      </c>
-      <c r="P44" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-02-13, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="U44" t="n">
-        <v>4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>2</v>
-      </c>
-      <c r="W44" t="n">
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
         <v>1</v>
       </c>
-      <c r="X44" t="n">
-        <v>0.5</v>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2647,48 +2647,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BUCARAMANGA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>PARQUE ORIENTE SOLEIL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución/Entregas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>Claudia Cruz</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luisa Henao</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
+          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
+          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -2714,12 +2738,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2728,80 +2752,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-28</t>
-        </is>
-      </c>
+          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2812,12 +2800,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2826,44 +2814,80 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-14, 2025-11-28</t>
+        </is>
+      </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32">
@@ -2874,12 +2898,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2888,84 +2912,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Jennifer Paola Lopez Vaca</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
+          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2976,50 +2960,98 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34">
@@ -3030,50 +3062,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>SABADO</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-11-01, 2025-11-03, 2025-11-08, 2025-11-10, 2025-11-15, 2025-11-17, 2025-11-22, 2025-11-24, 2025-11-29</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -3095,12 +3111,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3111,48 +3127,32 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Kelly Gutierrez</t>
-        </is>
-      </c>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2025-11-01, 2025-11-03, 2025-11-08, 2025-11-10, 2025-11-15, 2025-11-17, 2025-11-22, 2025-11-24, 2025-11-29</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -3161,37 +3161,21 @@
       <c r="P35" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2025-11-08, 2025-11-28</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3202,7 +3186,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3213,19 +3197,23 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orlando Iguaran</t>
+          <t>Kelly Gutierrez</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3235,22 +3223,22 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3261,46 +3249,46 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
+          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-27</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-08, 2025-11-28</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X36" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3311,20 +3299,16 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jhon Alexander Guarin Reina</t>
+          <t>Orlando Iguaran</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>MARTES</t>
@@ -3332,17 +3316,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3352,7 +3336,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3363,35 +3347,35 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
+          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2025-11-12, 2025-11-26</t>
+          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="38">
@@ -3402,50 +3386,98 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2025-11-12, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+        </is>
+      </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3456,12 +3488,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3470,77 +3502,33 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3554,7 +3542,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3570,7 +3558,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
+          <t>Zuri Andreina Orduz Sepulveda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -3581,48 +3569,64 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
-        </is>
-      </c>
       <c r="O40" t="n">
         <v>4</v>
       </c>
       <c r="P40" t="n">
         <v>4</v>
       </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3636,12 +3640,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3650,31 +3654,51 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
@@ -3698,100 +3722,58 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>2025-11-12, 2025-11-19, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2025-11-13, 2025-11-21, 2025-11-27</t>
-        </is>
-      </c>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3802,50 +3784,100 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2025-11-12, 2025-11-19, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2025-11-13, 2025-11-21, 2025-11-27</t>
+        </is>
+      </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
@@ -3856,12 +3888,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -3870,84 +3902,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Mauricio Andres Cervantes</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-21</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3958,7 +3942,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3974,13 +3958,13 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Mauricio Andres Cervantes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3990,17 +3974,17 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4010,7 +3994,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4021,22 +4005,22 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
+          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
+          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20</t>
+          <t>2025-11-06, 2025-11-14, 2025-11-21</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-29</t>
+          <t>2025-11-06, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="U45" t="n">
@@ -4060,7 +4044,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4071,74 +4055,176 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yenny Paola Munevar Peña</t>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-14, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>ZENTRAL</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
         <is>
           <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
-      <c r="O46" t="n">
-        <v>4</v>
-      </c>
-      <c r="P46" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q46" t="inlineStr">
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-27</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>2025-11-27</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="n">
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
         <v>1</v>
       </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
         <v>0.25</v>
       </c>
-      <c r="X46" t="n">
+      <c r="X47" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -575,8 +575,16 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
@@ -635,12 +643,12 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -651,35 +659,35 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-14, 2025-11-25, 2025-11-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-14, 2025-11-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -719,8 +727,16 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
@@ -773,7 +789,11 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -845,12 +865,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -861,22 +881,22 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-12, 2025-11-26</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -929,8 +949,16 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
@@ -983,16 +1011,8 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
@@ -1063,12 +1083,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1079,22 +1099,22 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2025-11-10, 2025-11-24</t>
+          <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-19</t>
+          <t>2026-02-04, 2026-02-19</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1167,12 +1187,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1183,31 +1203,31 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -1265,12 +1285,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1281,31 +1301,35 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2025-11-11, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-17</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -1347,14 +1371,10 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2025-11-10, 2025-11-14</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2025-11-10, 2025-11-14</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
@@ -1417,12 +1437,12 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1433,31 +1453,35 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
       <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="n">
         <v>1</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
         <v>0.25</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1507,12 +1531,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1523,31 +1547,35 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -1601,12 +1629,12 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -1617,31 +1645,35 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
+          <t>2026-02-26, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
@@ -1681,16 +1713,8 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2025-11-13, 2025-11-21</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
@@ -1745,12 +1769,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -1825,12 +1849,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1841,35 +1865,35 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-19, 2025-11-26</t>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-18, 2025-11-21, 2025-11-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2025-11-19, 2025-11-26</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-21, 2025-11-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1927,12 +1951,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1943,35 +1967,35 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-20</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-20</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2021,12 +2045,12 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -2037,31 +2061,35 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -2157,14 +2185,10 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
@@ -2235,12 +2259,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2251,35 +2275,35 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-17, 2025-11-19, 2025-11-27</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-17, 2025-11-20</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2025-11-19, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-02-06, 2026-02-20</t>
         </is>
       </c>
       <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" t="n">
         <v>2</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>1</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>0.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="24">
@@ -2319,7 +2343,11 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2373,7 +2401,11 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
@@ -2431,8 +2463,16 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
@@ -2503,12 +2543,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2519,22 +2559,22 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="U27" t="n">
@@ -2597,12 +2637,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2613,35 +2653,35 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2025-11-11, 2025-11-14, 2025-11-18, 2025-11-21, 2025-11-28</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2025-11-21, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2025-11-14, 2025-11-21, 2025-11-28</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="X28" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="29">
@@ -2691,12 +2731,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -2707,27 +2747,35 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-12, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
@@ -2769,12 +2817,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -2843,12 +2891,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2859,32 +2907,32 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
         <v>3</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X31" t="n">
         <v>0.75</v>
@@ -2927,16 +2975,8 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="n">
@@ -3007,12 +3047,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -3023,35 +3063,35 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="U33" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3</v>
+      </c>
+      <c r="W33" t="n">
         <v>1</v>
       </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X33" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="34">
@@ -3091,7 +3131,11 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -3147,16 +3191,16 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-03, 2025-11-08, 2025-11-10, 2025-11-15, 2025-11-17, 2025-11-22, 2025-11-24, 2025-11-29</t>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
         <v>4</v>
@@ -3233,12 +3277,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3249,35 +3293,31 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2025-11-08, 2025-11-28</t>
-        </is>
-      </c>
+          <t>2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3331,12 +3371,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3347,35 +3387,35 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-25</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-02-05, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X37" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="38">
@@ -3433,12 +3473,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -3449,32 +3489,32 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2025-11-12, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>4</v>
       </c>
       <c r="W38" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -3517,8 +3557,16 @@
       <c r="P39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
@@ -3589,12 +3637,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -3605,31 +3653,35 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>2026-02-11, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="41">
@@ -3683,12 +3735,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3697,21 +3749,37 @@
       <c r="P41" t="n">
         <v>4</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3753,12 +3821,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -3833,12 +3901,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -3849,35 +3917,35 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2025-11-12, 2025-11-19, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2025-11-13, 2025-11-21, 2025-11-27</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W43" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3989,12 +4057,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4005,35 +4073,35 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-21</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-06, 2026-02-26</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46">
@@ -4091,12 +4159,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -4107,22 +4175,22 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-29</t>
+          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="U46" t="n">
@@ -4185,12 +4253,12 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -4201,31 +4269,35 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-02-13, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U47" t="n">
+        <v>4</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
